--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>522.0</v>
+        <v>524.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -155,7 +155,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>740.0</v>
+        <v>744.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>524.0</v>
+        <v>526.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>
@@ -367,7 +367,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="F2" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>744.0</v>
+        <v>748.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>526.0</v>
+        <v>527.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -155,7 +155,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -181,7 +181,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>73.0</v>
+        <v>75.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>748.0</v>
+        <v>752.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>527.0</v>
+        <v>529.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>752.0</v>
+        <v>753.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -155,7 +155,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>753.0</v>
+        <v>754.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -367,7 +367,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
       <c r="F2" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="17">
   <si>
     <t>Area</t>
   </si>
@@ -181,7 +181,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>754.0</v>
+        <v>758.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -233,13 +233,13 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>77.0</v>
+        <v>158.0</v>
       </c>
       <c r="G5" t="n">
         <v>52.0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6">
@@ -259,13 +259,13 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>98.0</v>
+        <v>361.0</v>
       </c>
       <c r="G6" t="n">
         <v>19.0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="7">
@@ -285,13 +285,13 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>529.0</v>
+        <v>1087.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="8">
@@ -390,7 +390,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="F3" t="n">
         <v>10.0</v>
@@ -426,6 +426,9 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -448,6 +451,9 @@
       <c r="F2" t="n">
         <v>0.0</v>
       </c>
+      <c r="G2" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -463,9 +469,12 @@
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>1581.0</v>
+        <v>2270.0</v>
       </c>
       <c r="F3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G3" t="n">
         <v>12.0</v>
       </c>
     </row>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>758.0</v>
+        <v>759.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1087.0</v>
+        <v>1088.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>759.0</v>
+        <v>763.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -259,7 +259,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>361.0</v>
+        <v>362.0</v>
       </c>
       <c r="G6" t="n">
         <v>19.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1088.0</v>
+        <v>1091.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>
@@ -367,7 +367,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F2" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -155,7 +155,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>87.0</v>
+        <v>89.0</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>763.0</v>
+        <v>764.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1091.0</v>
+        <v>1092.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>
@@ -367,10 +367,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -259,7 +259,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>362.0</v>
+        <v>363.0</v>
       </c>
       <c r="G6" t="n">
         <v>19.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1092.0</v>
+        <v>1096.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>
@@ -370,10 +370,10 @@
         <v>18.0</v>
       </c>
       <c r="F2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G2" t="n">
         <v>7.0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="3">

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -155,7 +155,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>89.0</v>
+        <v>96.0</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -187,7 +187,7 @@
         <v>0.0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="4">
@@ -207,13 +207,13 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>764.0</v>
+        <v>767.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="5">
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1096.0</v>
+        <v>1098.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>
@@ -370,10 +370,10 @@
         <v>18.0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="3">

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1098.0</v>
+        <v>1100.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>767.0</v>
+        <v>770.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1100.0</v>
+        <v>1102.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>770.0</v>
+        <v>771.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -259,7 +259,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>363.0</v>
+        <v>364.0</v>
       </c>
       <c r="G6" t="n">
         <v>19.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -155,7 +155,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>771.0</v>
+        <v>772.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1102.0</v>
+        <v>1104.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -155,7 +155,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>97.0</v>
+        <v>111.0</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>772.0</v>
+        <v>774.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -233,13 +233,13 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>158.0</v>
+        <v>159.0</v>
       </c>
       <c r="G5" t="n">
         <v>52.0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -259,7 +259,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>364.0</v>
+        <v>368.0</v>
       </c>
       <c r="G6" t="n">
         <v>19.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1104.0</v>
+        <v>1107.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>
@@ -370,7 +370,7 @@
         <v>18.0</v>
       </c>
       <c r="F2" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -34,10 +34,10 @@
     <t>Negativo</t>
   </si>
   <si>
+    <t>Non idoneo</t>
+  </si>
+  <si>
     <t>Positivo</t>
-  </si>
-  <si>
-    <t>Non idoneo</t>
   </si>
   <si>
     <t>La</t>
@@ -161,7 +161,7 @@
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
@@ -184,10 +184,10 @@
         <v>76.0</v>
       </c>
       <c r="G3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="4">
@@ -210,10 +210,10 @@
         <v>774.0</v>
       </c>
       <c r="G4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H4" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="5">
@@ -236,10 +236,10 @@
         <v>159.0</v>
       </c>
       <c r="G5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H5" t="n">
         <v>52.0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -262,10 +262,10 @@
         <v>368.0</v>
       </c>
       <c r="G6" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H6" t="n">
         <v>19.0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>7.0</v>
       </c>
     </row>
     <row r="7">
@@ -288,10 +288,10 @@
         <v>1107.0</v>
       </c>
       <c r="G7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H7" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="8">
@@ -347,10 +347,10 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
         <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2">
@@ -426,10 +426,10 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
         <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2">

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>774.0</v>
+        <v>777.0</v>
       </c>
       <c r="G4" t="n">
         <v>3.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -181,10 +181,10 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H3" t="n">
         <v>0.0</v>
@@ -207,10 +207,10 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>777.0</v>
+        <v>778.0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H4" t="n">
         <v>2.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1107.0</v>
+        <v>1109.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -367,10 +367,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>18.0</v>
+        <v>24.0</v>
       </c>
       <c r="F2" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -34,10 +34,10 @@
     <t>Negativo</t>
   </si>
   <si>
+    <t>Positivo</t>
+  </si>
+  <si>
     <t>Non idoneo</t>
-  </si>
-  <si>
-    <t>Positivo</t>
   </si>
   <si>
     <t>La</t>
@@ -155,13 +155,13 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -184,10 +184,10 @@
         <v>77.0</v>
       </c>
       <c r="G3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H3" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>778.0</v>
+        <v>779.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -233,13 +233,13 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0</v>
+        <v>52.0</v>
       </c>
       <c r="H5" t="n">
-        <v>52.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6">
@@ -259,13 +259,13 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>368.0</v>
+        <v>369.0</v>
       </c>
       <c r="G6" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="H6" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>19.0</v>
       </c>
     </row>
     <row r="7">
@@ -288,10 +288,10 @@
         <v>1109.0</v>
       </c>
       <c r="G7" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="H7" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="8">
@@ -347,10 +347,10 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2">
@@ -367,10 +367,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>
@@ -426,10 +426,10 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2">

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -155,7 +155,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -181,7 +181,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>779.0</v>
+        <v>781.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -259,7 +259,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>369.0</v>
+        <v>371.0</v>
       </c>
       <c r="G6" t="n">
         <v>19.0</v>
@@ -285,13 +285,13 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1109.0</v>
+        <v>1112.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>781.0</v>
+        <v>782.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1112.0</v>
+        <v>1113.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -207,7 +207,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>782.0</v>
+        <v>783.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -233,7 +233,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>160.0</v>
+        <v>161.0</v>
       </c>
       <c r="G5" t="n">
         <v>52.0</v>
@@ -259,7 +259,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>371.0</v>
+        <v>372.0</v>
       </c>
       <c r="G6" t="n">
         <v>19.0</v>
@@ -285,7 +285,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1113.0</v>
+        <v>1114.0</v>
       </c>
       <c r="G7" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -367,10 +367,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="18">
   <si>
     <t>Area</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>Roma</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
   </si>
   <si>
     <t>Viterbo</t>
@@ -152,10 +155,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>113.0</v>
+        <v>115.0</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -178,7 +181,7 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
         <v>79.0</v>
@@ -204,10 +207,10 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>783.0</v>
+        <v>785.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -227,19 +230,19 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>161.0</v>
+        <v>1.0</v>
       </c>
       <c r="G5" t="n">
-        <v>52.0</v>
+        <v>0.0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -259,13 +262,13 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>372.0</v>
+        <v>162.0</v>
       </c>
       <c r="G6" t="n">
-        <v>19.0</v>
+        <v>52.0</v>
       </c>
       <c r="H6" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="7">
@@ -285,13 +288,13 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>1114.0</v>
+        <v>372.0</v>
       </c>
       <c r="G7" t="n">
-        <v>6.0</v>
+        <v>19.0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="8">
@@ -305,18 +308,44 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
+        <v>1114.0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="H8" t="n">
         <v>1.0</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H8" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -210,7 +210,7 @@
         <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>785.0</v>
+        <v>786.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -314,7 +314,7 @@
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>1114.0</v>
+        <v>1115.0</v>
       </c>
       <c r="G8" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -210,7 +210,7 @@
         <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>786.0</v>
+        <v>790.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -314,7 +314,7 @@
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>1115.0</v>
+        <v>1116.0</v>
       </c>
       <c r="G8" t="n">
         <v>6.0</v>
@@ -396,10 +396,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -210,7 +210,7 @@
         <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>790.0</v>
+        <v>791.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -314,7 +314,7 @@
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>1116.0</v>
+        <v>1118.0</v>
       </c>
       <c r="G8" t="n">
         <v>6.0</v>
@@ -396,7 +396,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="F2" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -396,10 +396,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="F2" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -399,7 +399,7 @@
         <v>33.0</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -210,7 +210,7 @@
         <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>791.0</v>
+        <v>794.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -262,7 +262,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
       <c r="G6" t="n">
         <v>52.0</v>
@@ -314,7 +314,7 @@
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>1118.0</v>
+        <v>1119.0</v>
       </c>
       <c r="G8" t="n">
         <v>6.0</v>
@@ -396,10 +396,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="F2" t="n">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -210,7 +210,7 @@
         <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>794.0</v>
+        <v>797.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -396,10 +396,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>36.0</v>
+        <v>50.0</v>
       </c>
       <c r="F2" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -158,7 +158,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>115.0</v>
+        <v>93.0</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -314,7 +314,7 @@
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>1119.0</v>
+        <v>1120.0</v>
       </c>
       <c r="G8" t="n">
         <v>6.0</v>
@@ -396,10 +396,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>
@@ -475,7 +475,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>768.0</v>
+        <v>790.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -158,7 +158,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G2" t="n">
         <v>1.0</v>
@@ -210,7 +210,7 @@
         <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>797.0</v>
+        <v>798.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -314,7 +314,7 @@
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>1120.0</v>
+        <v>1124.0</v>
       </c>
       <c r="G8" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -288,7 +288,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>372.0</v>
+        <v>373.0</v>
       </c>
       <c r="G7" t="n">
         <v>19.0</v>
@@ -314,7 +314,7 @@
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>1124.0</v>
+        <v>1125.0</v>
       </c>
       <c r="G8" t="n">
         <v>6.0</v>
@@ -396,10 +396,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>51.0</v>
+        <v>53.0</v>
       </c>
       <c r="F2" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -184,7 +184,7 @@
         <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -210,7 +210,7 @@
         <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>798.0</v>
+        <v>801.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -288,7 +288,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>373.0</v>
+        <v>375.0</v>
       </c>
       <c r="G7" t="n">
         <v>19.0</v>
@@ -314,7 +314,7 @@
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>1125.0</v>
+        <v>1127.0</v>
       </c>
       <c r="G8" t="n">
         <v>6.0</v>
@@ -399,7 +399,7 @@
         <v>53.0</v>
       </c>
       <c r="F2" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -210,7 +210,7 @@
         <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>801.0</v>
+        <v>802.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -314,7 +314,7 @@
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>1127.0</v>
+        <v>1128.0</v>
       </c>
       <c r="G8" t="n">
         <v>6.0</v>

--- a/Download/Cinghiali_ZP.xlsx
+++ b/Download/Cinghiali_ZP.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="18">
   <si>
     <t>Area</t>
   </si>
@@ -210,7 +210,7 @@
         <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>802.0</v>
+        <v>804.0</v>
       </c>
       <c r="G4" t="n">
         <v>2.0</v>
@@ -256,19 +256,19 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>163.0</v>
+        <v>1.0</v>
       </c>
       <c r="G6" t="n">
-        <v>52.0</v>
+        <v>0.0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -285,16 +285,16 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>375.0</v>
+        <v>164.0</v>
       </c>
       <c r="G7" t="n">
-        <v>19.0</v>
+        <v>52.0</v>
       </c>
       <c r="H7" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">
@@ -311,16 +311,16 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>1128.0</v>
+        <v>375.0</v>
       </c>
       <c r="G8" t="n">
-        <v>6.0</v>
+        <v>19.0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="9">
@@ -334,18 +334,44 @@
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0</v>
+        <v>1129.0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H9" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -396,10 +422,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="F2" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
       <c r="G2" t="n">
         <v>8.0</v>
@@ -422,7 +448,7 @@
         <v>29.0</v>
       </c>
       <c r="F3" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="G3" t="n">
         <v>4.0</v>
